--- a/Compititor's_Price/Mannok_Prices/Mannok_Prices_01-10-2025.xlsx
+++ b/Compititor's_Price/Mannok_Prices/Mannok_Prices_01-10-2025.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.45</t>
+          <t>£10.35</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.45</t>
+          <t>£10.35</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.97</t>
+          <t>£11.80</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.97</t>
+          <t>£11.80</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -567,12 +567,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£15.25</t>
+          <t>£15.10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.25</t>
+          <t>£15.10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£19.80</t>
+          <t>£19.60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£19.80</t>
+          <t>£19.60</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£21.70</t>
+          <t>£21.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£21.70</t>
+          <t>£21.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£21.90</t>
+          <t>£21.60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£21.90</t>
+          <t>£21.60</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -777,12 +777,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£25.15</t>
+          <t>£24.86</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.15</t>
+          <t>£24.86</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£27.25</t>
+          <t>£26.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£27.25</t>
+          <t>£26.95</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£26.79</t>
+          <t>£26.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.79</t>
+          <t>£26.50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£35.55</t>
+          <t>£35.13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£35.55</t>
+          <t>£35.13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£32.89</t>
+          <t>£32.49</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£32.89</t>
+          <t>£32.49</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£39.76</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£39.76</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£40.95</t>
+          <t>£40.39</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£40.95</t>
+          <t>£40.39</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£40.85</t>
+          <t>£40.45</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£40.85</t>
+          <t>£40.45</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
